--- a/artfynd/Kläpptjärnen artfynd.xlsx
+++ b/artfynd/Kläpptjärnen artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89046267</v>
+        <v>89046266</v>
       </c>
       <c r="B2" t="n">
-        <v>92529</v>
+        <v>93222</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,14 +715,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Blåberget, 1,6 km om toppen, Ång</t>
+          <t>Blåberget, SO om, S om Snottertjärnen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>689819</v>
+        <v>689292</v>
       </c>
       <c r="R2" t="n">
-        <v>7093805</v>
+        <v>7093013</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,7 +768,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog</t>
+          <t>150-årig gles sandtallskog, i stigkant</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89046265</v>
+        <v>96972035</v>
       </c>
       <c r="B3" t="n">
-        <v>92551</v>
+        <v>90932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,43 +801,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Blåberget, SO om, S om Snottertjärnen, Ång</t>
+          <t>Blåberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>689428</v>
+        <v>689061</v>
       </c>
       <c r="R3" t="n">
-        <v>7093161</v>
+        <v>7094549</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,12 +858,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,23 +872,19 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>150-årig gles sandtallskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -905,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89046272</v>
+        <v>96972031</v>
       </c>
       <c r="B4" t="n">
-        <v>92551</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,43 +906,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Blåberget, SO om, öster om Snottertjärnen, Ång</t>
+          <t>Blåberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>689430</v>
+        <v>689135</v>
       </c>
       <c r="R4" t="n">
-        <v>7093353</v>
+        <v>7094668</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,12 +963,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,23 +977,19 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>150-årig sandtallskog, i renbetad västsluttning</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1020,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89046266</v>
+        <v>96971940</v>
       </c>
       <c r="B5" t="n">
-        <v>92560</v>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,43 +1011,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3100</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Blåberget, SO om, S om Snottertjärnen, Ång</t>
+          <t>Blåberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>689292</v>
+        <v>689265</v>
       </c>
       <c r="R5" t="n">
-        <v>7093013</v>
+        <v>7094450</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,12 +1068,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,23 +1082,19 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>150-årig gles sandtallskog, i stigkant</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1135,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>87755103</v>
+        <v>89046264</v>
       </c>
       <c r="B6" t="n">
-        <v>92529</v>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1146,37 +1116,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Blåberget, Ång</t>
+          <t>Blåberget, SO om, S om Snottertjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>689795</v>
+        <v>689466</v>
       </c>
       <c r="R6" t="n">
-        <v>7093764</v>
+        <v>7093103</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,12 +1170,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-08-23</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-08-23</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,19 +1184,31 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog, i västsluttning</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov gammal tallåga</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1240,48 +1219,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>87755059</v>
+        <v>89046282</v>
       </c>
       <c r="B7" t="n">
-        <v>90001</v>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6276</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Blåberget, Ång</t>
+          <t>Blåberget, SO om, öster om Snottertjärnen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>689771</v>
+        <v>689476</v>
       </c>
       <c r="R7" t="n">
-        <v>7093769</v>
+        <v>7093501</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,12 +1284,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-08-23</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-08-23</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,19 +1298,31 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog, i västsluttning</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>1 substratenheter # rest av hård gammal tallåga</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1345,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89046263</v>
+        <v>89046280</v>
       </c>
       <c r="B8" t="n">
-        <v>90001</v>
+        <v>90674</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1356,21 +1344,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6276</v>
+        <v>1596</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,14 +1373,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Blåberget, SO om, S om Snottertjärnen, Ång</t>
+          <t>Blåberget, SO om, öster om Snottertjärnen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>689467</v>
+        <v>689517</v>
       </c>
       <c r="R8" t="n">
-        <v>7093174</v>
+        <v>7093383</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,7 +1426,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog, i västsluttning</t>
+          <t>150-årig sandtallskog, i renbetad nordvästsluttning</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1460,48 +1448,54 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96971940</v>
+        <v>89046261</v>
       </c>
       <c r="B9" t="n">
-        <v>91265</v>
+        <v>93213</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>2059</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Blåberget, Ång</t>
+          <t>Blåberget, SO om, S om Snottertjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>689265</v>
+        <v>689418</v>
       </c>
       <c r="R9" t="n">
-        <v>7094450</v>
+        <v>7093024</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1528,12 +1522,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1542,19 +1536,23 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog, stigkant i västsluttning</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1565,48 +1563,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96972035</v>
+        <v>89046265</v>
       </c>
       <c r="B10" t="n">
-        <v>90283</v>
+        <v>93213</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1962</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Blåberget, Ång</t>
+          <t>Blåberget, SO om, S om Snottertjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>689061</v>
+        <v>689428</v>
       </c>
       <c r="R10" t="n">
-        <v>7094549</v>
+        <v>7093161</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,12 +1637,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1647,19 +1651,23 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>150-årig gles sandtallskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1670,48 +1678,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>87755085</v>
+        <v>89046272</v>
       </c>
       <c r="B11" t="n">
-        <v>78647</v>
+        <v>93213</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Blåberget, Ång</t>
+          <t>Blåberget, SO om, öster om Snottertjärnen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>689857</v>
+        <v>689430</v>
       </c>
       <c r="R11" t="n">
-        <v>7093888</v>
+        <v>7093353</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,12 +1752,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-08-23</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-08-23</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1752,19 +1766,23 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog, i renbetad västsluttning</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1775,10 +1793,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>89046270</v>
+        <v>89046262</v>
       </c>
       <c r="B12" t="n">
-        <v>92529</v>
+        <v>93191</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,14 +1833,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Blåberget, 1,6 km om toppen, Ång</t>
+          <t>Blåberget, SO om, S om Snottertjärnen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>689854</v>
+        <v>689418</v>
       </c>
       <c r="R12" t="n">
-        <v>7093870</v>
+        <v>7093024</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,7 +1886,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog</t>
+          <t>150-årig sandtallskog, stigkant i västsluttning</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1890,10 +1908,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>89046274</v>
+        <v>89046273</v>
       </c>
       <c r="B13" t="n">
-        <v>92529</v>
+        <v>93191</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1934,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>689462</v>
+        <v>689482</v>
       </c>
       <c r="R13" t="n">
-        <v>7093351</v>
+        <v>7093418</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1983,7 +2001,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog, i renbetad nordvästsluttning</t>
+          <t>150-årig sandtallskog, i renbetad västsluttning</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2005,48 +2023,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>96972031</v>
+        <v>89046274</v>
       </c>
       <c r="B14" t="n">
-        <v>92535</v>
+        <v>93191</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Blåberget, Ång</t>
+          <t>Blåberget, SO om, öster om Snottertjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>689135</v>
+        <v>689462</v>
       </c>
       <c r="R14" t="n">
-        <v>7094668</v>
+        <v>7093351</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,12 +2097,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2087,19 +2111,23 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog, i renbetad nordvästsluttning</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2110,10 +2138,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>89046281</v>
+        <v>89046263</v>
       </c>
       <c r="B15" t="n">
-        <v>90001</v>
+        <v>90691</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2150,14 +2178,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Blåberget, SO om, öster om Snottertjärnen, Ång</t>
+          <t>Blåberget, SO om, S om Snottertjärnen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>689520</v>
+        <v>689467</v>
       </c>
       <c r="R15" t="n">
-        <v>7093411</v>
+        <v>7093174</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2203,7 +2231,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog, i renbetad västsluttning</t>
+          <t>150-årig sandtallskog, i västsluttning</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2225,10 +2253,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>89046280</v>
+        <v>89046276</v>
       </c>
       <c r="B16" t="n">
-        <v>89979</v>
+        <v>90691</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,26 +2264,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1596</v>
+        <v>6276</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2269,10 +2297,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>689517</v>
+        <v>689471</v>
       </c>
       <c r="R16" t="n">
-        <v>7093383</v>
+        <v>7093298</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2318,7 +2346,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog, i renbetad nordvästsluttning</t>
+          <t>150-årig sandtallskog, i renbetad västsluttning</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2340,10 +2368,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>89046276</v>
+        <v>89046277</v>
       </c>
       <c r="B17" t="n">
-        <v>90001</v>
+        <v>90691</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2370,7 +2398,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2384,10 +2412,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>689471</v>
+        <v>689500</v>
       </c>
       <c r="R17" t="n">
-        <v>7093298</v>
+        <v>7093337</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2455,32 +2483,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>89046278</v>
+        <v>89046281</v>
       </c>
       <c r="B18" t="n">
-        <v>90749</v>
+        <v>90691</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>256703</v>
+        <v>6276</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2499,10 +2527,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>689503</v>
+        <v>689520</v>
       </c>
       <c r="R18" t="n">
-        <v>7093351</v>
+        <v>7093411</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2543,13 +2571,12 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog, i renbetad nordvästsluttning</t>
+          <t>150-årig sandtallskog, i renbetad västsluttning</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2571,10 +2598,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>16846931</v>
+        <v>89046275</v>
       </c>
       <c r="B19" t="n">
-        <v>91263</v>
+        <v>91402</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2582,34 +2609,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>256703</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kläpptjärn, Ång</t>
+          <t>Blåberget, SO om, öster om Snottertjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>689905</v>
+        <v>689460</v>
       </c>
       <c r="R19" t="n">
-        <v>7093802</v>
+        <v>7093210</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2636,12 +2672,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2013-07-08</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2013-07-08</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2650,28 +2686,24 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>granskog</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>150-årig sandtallskog, i renbetad nordvästsluttning</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Niina Sallmén</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Niina Sallmén, sofia nordin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2682,10 +2714,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>89046282</v>
+        <v>89046278</v>
       </c>
       <c r="B20" t="n">
-        <v>78647</v>
+        <v>91402</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2693,34 +2725,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>256703</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Blåberget, SO om, öster om Snottertjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>689476</v>
+        <v>689503</v>
       </c>
       <c r="R20" t="n">
-        <v>7093501</v>
+        <v>7093351</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2761,20 +2802,13 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog, i västsluttning</t>
-        </is>
-      </c>
-      <c r="AN20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>1 substratenheter # rest av hård gammal tallåga</t>
+          <t>150-årig sandtallskog, i renbetad nordvästsluttning</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2796,10 +2830,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>89046273</v>
+        <v>87755085</v>
       </c>
       <c r="B21" t="n">
-        <v>92529</v>
+        <v>78993</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2807,43 +2841,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Blåberget, SO om, öster om Snottertjärnen, Ång</t>
+          <t>Blåberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>689482</v>
+        <v>689857</v>
       </c>
       <c r="R21" t="n">
-        <v>7093418</v>
+        <v>7093888</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2870,12 +2898,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2020-08-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2020-08-23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2884,23 +2912,19 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>150-årig sandtallskog, i renbetad västsluttning</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2911,32 +2935,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>89046271</v>
+        <v>89046268</v>
       </c>
       <c r="B22" t="n">
-        <v>92547</v>
+        <v>93213</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2955,10 +2979,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>689833</v>
+        <v>689850</v>
       </c>
       <c r="R22" t="n">
-        <v>7093948</v>
+        <v>7093829</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3026,48 +3050,54 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>87755147</v>
+        <v>112367952</v>
       </c>
       <c r="B23" t="n">
-        <v>92527</v>
+        <v>93213</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Blåberget, Ång</t>
+          <t>Lögdeälven-Drakryggen m omnejd, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>689819</v>
+        <v>689757</v>
       </c>
       <c r="R23" t="n">
-        <v>7093761</v>
+        <v>7094522</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3094,12 +3124,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2020-08-23</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2020-08-23</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3108,77 +3138,70 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Sandtallskogsprojektet 2023, Västerbottens län</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>89046277</v>
+        <v>87755147</v>
       </c>
       <c r="B24" t="n">
-        <v>90001</v>
+        <v>93189</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Blåberget, SO om, öster om Snottertjärnen, Ång</t>
+          <t>Blåberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>689500</v>
+        <v>689819</v>
       </c>
       <c r="R24" t="n">
-        <v>7093337</v>
+        <v>7093761</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3205,12 +3228,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2020-08-23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2020-08-23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3219,23 +3242,19 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>150-årig sandtallskog, i renbetad västsluttning</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3246,54 +3265,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>89046275</v>
+        <v>87755103</v>
       </c>
       <c r="B25" t="n">
-        <v>90749</v>
+        <v>93191</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>256703</v>
+        <v>4362</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Blåberget, SO om, öster om Snottertjärnen, Ång</t>
+          <t>Blåberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>689460</v>
+        <v>689795</v>
       </c>
       <c r="R25" t="n">
-        <v>7093210</v>
+        <v>7093764</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3320,12 +3333,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2020-08-23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2020-08-23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3338,20 +3351,15 @@
       <c r="AG25" t="b">
         <v>0</v>
       </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>150-årig sandtallskog, i renbetad nordvästsluttning</t>
-        </is>
-      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3362,10 +3370,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>89046262</v>
+        <v>89046267</v>
       </c>
       <c r="B26" t="n">
-        <v>92529</v>
+        <v>93191</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3402,14 +3410,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Blåberget, SO om, S om Snottertjärnen, Ång</t>
+          <t>Blåberget, 1,6 km om toppen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>689418</v>
+        <v>689819</v>
       </c>
       <c r="R26" t="n">
-        <v>7093024</v>
+        <v>7093805</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3455,7 +3463,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog, stigkant i västsluttning</t>
+          <t>140-årig sandtallskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3477,32 +3485,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>89046269</v>
+        <v>89046270</v>
       </c>
       <c r="B27" t="n">
-        <v>90001</v>
+        <v>93191</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3521,10 +3529,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>689852</v>
+        <v>689854</v>
       </c>
       <c r="R27" t="n">
-        <v>7093854</v>
+        <v>7093870</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3592,10 +3600,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>89046268</v>
+        <v>89046271</v>
       </c>
       <c r="B28" t="n">
-        <v>92551</v>
+        <v>93209</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3603,21 +3611,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3636,10 +3644,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>689850</v>
+        <v>689833</v>
       </c>
       <c r="R28" t="n">
-        <v>7093829</v>
+        <v>7093948</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3707,54 +3715,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>89046261</v>
+        <v>87755059</v>
       </c>
       <c r="B29" t="n">
-        <v>92551</v>
+        <v>90691</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Blåberget, SO om, S om Snottertjärnen, Ång</t>
+          <t>Blåberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>689418</v>
+        <v>689771</v>
       </c>
       <c r="R29" t="n">
-        <v>7093024</v>
+        <v>7093769</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3781,12 +3783,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2020-08-23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2020-08-23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3795,28 +3797,548 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>150-årig sandtallskog, stigkant i västsluttning</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>89046269</v>
+      </c>
+      <c r="B30" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Blåberget, 1,6 km om toppen, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>689852</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7093854</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2020-08-31</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2020-08-31</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>140-årig sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
           <t>Magnus Andersson</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
+      <c r="AX30" t="inlineStr">
         <is>
           <t>Magnus Andersson</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr">
+      <c r="AY30" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>112368024</v>
+      </c>
+      <c r="B31" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lögdeälven-Drakryggen m omnejd, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>690157</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7093462</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>112367956</v>
+      </c>
+      <c r="B32" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lögdeälven-Drakryggen m omnejd, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>690157</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7093465</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>112367987</v>
+      </c>
+      <c r="B33" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lögdeälven-Drakryggen m omnejd, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>690160</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7093472</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>112367930</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lögdeälven-Drakryggen m omnejd, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>689998</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7093980</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>barksprätt, ytliga ringhack gran</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, Västerbottens län</t>
         </is>
       </c>
     </row>

--- a/artfynd/Kläpptjärnen artfynd.xlsx
+++ b/artfynd/Kläpptjärnen artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1105,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89046264</v>
+        <v>133000740</v>
       </c>
       <c r="B6" t="n">
-        <v>78993</v>
+        <v>79130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1116,34 +1116,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Blåberget, SO om, S om Snottertjärnen, Ång</t>
+          <t>Mattedalen, Mattedalen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>689466</v>
+        <v>689065</v>
       </c>
       <c r="R6" t="n">
-        <v>7093103</v>
+        <v>7094118</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,12 +1170,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1186,43 +1196,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>150-årig sandtallskog, i västsluttning</t>
-        </is>
-      </c>
-      <c r="AN6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>1 substratenheter # grov gammal tallåga</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89046282</v>
+        <v>133000698</v>
       </c>
       <c r="B7" t="n">
-        <v>78993</v>
+        <v>79992</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1230,34 +1223,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Blåberget, SO om, öster om Snottertjärnen, Ång</t>
+          <t>Mattedalen, Mattedalen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>689476</v>
+        <v>689065</v>
       </c>
       <c r="R7" t="n">
-        <v>7093501</v>
+        <v>7094118</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,12 +1277,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1300,87 +1303,61 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>150-årig sandtallskog, i västsluttning</t>
-        </is>
-      </c>
-      <c r="AN7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>1 substratenheter # rest av hård gammal tallåga</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89046280</v>
+        <v>133001416</v>
       </c>
       <c r="B8" t="n">
-        <v>90674</v>
+        <v>57969</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1596</v>
+        <v>102977</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Blåberget, SO om, öster om Snottertjärnen, Ång</t>
+          <t>Mattedalen, Mattedalen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>689517</v>
+        <v>689065</v>
       </c>
       <c r="R8" t="n">
-        <v>7093383</v>
+        <v>7094118</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,12 +1384,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,79 +1410,61 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>150-årig sandtallskog, i renbetad nordvästsluttning</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89046261</v>
+        <v>133000003</v>
       </c>
       <c r="B9" t="n">
-        <v>93213</v>
+        <v>98066</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2059</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Blåberget, SO om, S om Snottertjärnen, Ång</t>
+          <t>Mattedalen, Mattedalen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>689418</v>
+        <v>689065</v>
       </c>
       <c r="R9" t="n">
-        <v>7093024</v>
+        <v>7094118</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,12 +1491,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,79 +1517,61 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>150-årig sandtallskog, stigkant i västsluttning</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89046265</v>
+        <v>132999566</v>
       </c>
       <c r="B10" t="n">
-        <v>93213</v>
+        <v>98060</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2059</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Blåberget, SO om, S om Snottertjärnen, Ång</t>
+          <t>Mattedalen, Mattedalen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>689428</v>
+        <v>689029</v>
       </c>
       <c r="R10" t="n">
-        <v>7093161</v>
+        <v>7094259</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,12 +1598,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,79 +1624,61 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>150-årig gles sandtallskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89046272</v>
+        <v>132999629</v>
       </c>
       <c r="B11" t="n">
-        <v>93213</v>
+        <v>98060</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2059</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Blåberget, SO om, öster om Snottertjärnen, Ång</t>
+          <t>Mattedalen, Mattedalen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>689430</v>
+        <v>689035</v>
       </c>
       <c r="R11" t="n">
-        <v>7093353</v>
+        <v>7094206</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1752,12 +1705,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>08:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1768,79 +1731,61 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>150-årig sandtallskog, i renbetad västsluttning</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>89046262</v>
+        <v>132999657</v>
       </c>
       <c r="B12" t="n">
-        <v>93191</v>
+        <v>98060</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Blåberget, SO om, S om Snottertjärnen, Ång</t>
+          <t>Mattedalen, Mattedalen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>689418</v>
+        <v>689044</v>
       </c>
       <c r="R12" t="n">
-        <v>7093024</v>
+        <v>7094177</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1867,12 +1812,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1883,79 +1838,61 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>150-årig sandtallskog, stigkant i västsluttning</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>89046273</v>
+        <v>132999729</v>
       </c>
       <c r="B13" t="n">
-        <v>93191</v>
+        <v>98060</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Blåberget, SO om, öster om Snottertjärnen, Ång</t>
+          <t>Mattedalen, Mattedalen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>689482</v>
+        <v>689062</v>
       </c>
       <c r="R13" t="n">
-        <v>7093418</v>
+        <v>7094144</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1982,12 +1919,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>08:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>08:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1998,79 +1945,61 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>150-årig sandtallskog, i renbetad västsluttning</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89046274</v>
+        <v>133001622</v>
       </c>
       <c r="B14" t="n">
-        <v>93191</v>
+        <v>98060</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Blåberget, SO om, öster om Snottertjärnen, Ång</t>
+          <t>Kläpptjärnen, Kläpptjärnen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>689462</v>
+        <v>689074</v>
       </c>
       <c r="R14" t="n">
-        <v>7093351</v>
+        <v>7094293</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2097,12 +2026,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2113,79 +2052,61 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>150-årig sandtallskog, i renbetad nordvästsluttning</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>89046263</v>
+        <v>133000728</v>
       </c>
       <c r="B15" t="n">
-        <v>90691</v>
+        <v>79131</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6276</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Blåberget, SO om, S om Snottertjärnen, Ång</t>
+          <t>Mattedalen, Mattedalen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>689467</v>
+        <v>689065</v>
       </c>
       <c r="R15" t="n">
-        <v>7093174</v>
+        <v>7094118</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2212,12 +2133,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2228,79 +2159,61 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>150-årig sandtallskog, i västsluttning</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>89046276</v>
+        <v>133001562</v>
       </c>
       <c r="B16" t="n">
-        <v>90691</v>
+        <v>79131</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6276</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Blåberget, SO om, öster om Snottertjärnen, Ång</t>
+          <t>Kläpptjärnen, Kläpptjärnen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>689471</v>
+        <v>689085</v>
       </c>
       <c r="R16" t="n">
-        <v>7093298</v>
+        <v>7094281</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2327,12 +2240,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,79 +2266,61 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>150-årig sandtallskog, i renbetad västsluttning</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>89046277</v>
+        <v>133000871</v>
       </c>
       <c r="B17" t="n">
-        <v>90691</v>
+        <v>79963</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6276</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Blåberget, SO om, öster om Snottertjärnen, Ång</t>
+          <t>Mattedalen, Mattedalen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>689500</v>
+        <v>689065</v>
       </c>
       <c r="R17" t="n">
-        <v>7093337</v>
+        <v>7094118</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2442,12 +2347,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2020-08-31</t>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2458,79 +2373,61 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>150-årig sandtallskog, i renbetad västsluttning</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Anton Albertsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Anton Albertsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>89046281</v>
+        <v>89046264</v>
       </c>
       <c r="B18" t="n">
-        <v>90691</v>
+        <v>78993</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6276</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Blåberget, SO om, öster om Snottertjärnen, Ång</t>
+          <t>Blåberget, SO om, S om Snottertjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>689520</v>
+        <v>689466</v>
       </c>
       <c r="R18" t="n">
-        <v>7093411</v>
+        <v>7093103</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2576,7 +2473,15 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog, i renbetad västsluttning</t>
+          <t>150-årig sandtallskog, i västsluttning</t>
+        </is>
+      </c>
+      <c r="AN18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov gammal tallåga</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2598,10 +2503,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>89046275</v>
+        <v>89046282</v>
       </c>
       <c r="B19" t="n">
-        <v>91402</v>
+        <v>78993</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,43 +2514,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>256703</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Blåberget, SO om, öster om Snottertjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>689460</v>
+        <v>689476</v>
       </c>
       <c r="R19" t="n">
-        <v>7093210</v>
+        <v>7093501</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2686,13 +2582,20 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>150-årig sandtallskog, i renbetad nordvästsluttning</t>
+          <t>150-årig sandtallskog, i västsluttning</t>
+        </is>
+      </c>
+      <c r="AN19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>1 substratenheter # rest av hård gammal tallåga</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2714,32 +2617,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>89046278</v>
+        <v>89046280</v>
       </c>
       <c r="B20" t="n">
-        <v>91402</v>
+        <v>90674</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>256703</v>
+        <v>1596</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2758,10 +2661,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>689503</v>
+        <v>689517</v>
       </c>
       <c r="R20" t="n">
-        <v>7093351</v>
+        <v>7093383</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2802,7 +2705,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2830,48 +2732,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>87755085</v>
+        <v>89046261</v>
       </c>
       <c r="B21" t="n">
-        <v>78993</v>
+        <v>93213</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Blåberget, Ång</t>
+          <t>Blåberget, SO om, S om Snottertjärnen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>689857</v>
+        <v>689418</v>
       </c>
       <c r="R21" t="n">
-        <v>7093888</v>
+        <v>7093024</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2898,12 +2806,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2020-08-23</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2020-08-23</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2912,19 +2820,23 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog, stigkant i västsluttning</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2935,7 +2847,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>89046268</v>
+        <v>89046265</v>
       </c>
       <c r="B22" t="n">
         <v>93213</v>
@@ -2975,14 +2887,14 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Blåberget, 1,6 km om toppen, Ång</t>
+          <t>Blåberget, SO om, S om Snottertjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>689850</v>
+        <v>689428</v>
       </c>
       <c r="R22" t="n">
-        <v>7093829</v>
+        <v>7093161</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3028,7 +2940,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog</t>
+          <t>150-årig gles sandtallskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3050,7 +2962,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112367952</v>
+        <v>89046272</v>
       </c>
       <c r="B23" t="n">
         <v>93213</v>
@@ -3080,24 +2992,24 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lögdeälven-Drakryggen m omnejd, Ång</t>
+          <t>Blåberget, SO om, öster om Snottertjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>689757</v>
+        <v>689430</v>
       </c>
       <c r="R23" t="n">
-        <v>7094522</v>
+        <v>7093353</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3124,12 +3036,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3140,30 +3052,35 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog, i renbetad västsluttning</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>Sandtallskogsprojektet 2023, Västerbottens län</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>87755147</v>
+        <v>89046262</v>
       </c>
       <c r="B24" t="n">
-        <v>93189</v>
+        <v>93191</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3171,37 +3088,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Blåberget, Ång</t>
+          <t>Blåberget, SO om, S om Snottertjärnen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>689819</v>
+        <v>689418</v>
       </c>
       <c r="R24" t="n">
-        <v>7093761</v>
+        <v>7093024</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3228,12 +3151,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2020-08-23</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2020-08-23</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3242,19 +3165,23 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog, stigkant i västsluttning</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3265,7 +3192,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>87755103</v>
+        <v>89046273</v>
       </c>
       <c r="B25" t="n">
         <v>93191</v>
@@ -3293,20 +3220,26 @@
           <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Blåberget, Ång</t>
+          <t>Blåberget, SO om, öster om Snottertjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>689795</v>
+        <v>689482</v>
       </c>
       <c r="R25" t="n">
-        <v>7093764</v>
+        <v>7093418</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3333,12 +3266,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2020-08-23</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2020-08-23</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3347,19 +3280,23 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog, i renbetad västsluttning</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3370,7 +3307,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>89046267</v>
+        <v>89046274</v>
       </c>
       <c r="B26" t="n">
         <v>93191</v>
@@ -3410,14 +3347,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Blåberget, 1,6 km om toppen, Ång</t>
+          <t>Blåberget, SO om, öster om Snottertjärnen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>689819</v>
+        <v>689462</v>
       </c>
       <c r="R26" t="n">
-        <v>7093805</v>
+        <v>7093351</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3463,7 +3400,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog</t>
+          <t>150-årig sandtallskog, i renbetad nordvästsluttning</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3485,32 +3422,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>89046270</v>
+        <v>89046263</v>
       </c>
       <c r="B27" t="n">
-        <v>93191</v>
+        <v>90691</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3525,14 +3462,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Blåberget, 1,6 km om toppen, Ång</t>
+          <t>Blåberget, SO om, S om Snottertjärnen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>689854</v>
+        <v>689467</v>
       </c>
       <c r="R27" t="n">
-        <v>7093870</v>
+        <v>7093174</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3578,7 +3515,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog</t>
+          <t>150-årig sandtallskog, i västsluttning</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3600,37 +3537,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>89046271</v>
+        <v>89046276</v>
       </c>
       <c r="B28" t="n">
-        <v>93209</v>
+        <v>90691</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4366</v>
+        <v>6276</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3640,14 +3577,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Blåberget, 1,6 km om toppen, Ång</t>
+          <t>Blåberget, SO om, öster om Snottertjärnen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>689833</v>
+        <v>689471</v>
       </c>
       <c r="R28" t="n">
-        <v>7093948</v>
+        <v>7093298</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3693,7 +3630,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog</t>
+          <t>150-årig sandtallskog, i renbetad västsluttning</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3715,7 +3652,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>87755059</v>
+        <v>89046277</v>
       </c>
       <c r="B29" t="n">
         <v>90691</v>
@@ -3743,20 +3680,26 @@
           <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Blåberget, Ång</t>
+          <t>Blåberget, SO om, öster om Snottertjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>689771</v>
+        <v>689500</v>
       </c>
       <c r="R29" t="n">
-        <v>7093769</v>
+        <v>7093337</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3783,12 +3726,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2020-08-23</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2020-08-23</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3797,19 +3740,23 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog, i renbetad västsluttning</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3820,7 +3767,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>89046269</v>
+        <v>89046281</v>
       </c>
       <c r="B30" t="n">
         <v>90691</v>
@@ -3860,14 +3807,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Blåberget, 1,6 km om toppen, Ång</t>
+          <t>Blåberget, SO om, öster om Snottertjärnen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>689852</v>
+        <v>689520</v>
       </c>
       <c r="R30" t="n">
-        <v>7093854</v>
+        <v>7093411</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3913,7 +3860,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>140-årig sandtallskog</t>
+          <t>150-årig sandtallskog, i renbetad västsluttning</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3935,10 +3882,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112368024</v>
+        <v>89046275</v>
       </c>
       <c r="B31" t="n">
-        <v>93197</v>
+        <v>91402</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3946,34 +3893,43 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>256703</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lögdeälven-Drakryggen m omnejd, Ång</t>
+          <t>Blåberget, SO om, öster om Snottertjärnen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>690157</v>
+        <v>689460</v>
       </c>
       <c r="R31" t="n">
-        <v>7093462</v>
+        <v>7093210</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4000,12 +3956,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4014,32 +3970,38 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog, i renbetad nordvästsluttning</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>Sandtallskogsprojektet 2023, Västerbottens län</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112367956</v>
+        <v>89046278</v>
       </c>
       <c r="B32" t="n">
-        <v>93209</v>
+        <v>91402</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4047,34 +4009,43 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4366</v>
+        <v>256703</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lögdeälven-Drakryggen m omnejd, Ång</t>
+          <t>Blåberget, SO om, öster om Snottertjärnen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>690157</v>
+        <v>689503</v>
       </c>
       <c r="R32" t="n">
-        <v>7093465</v>
+        <v>7093351</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4101,12 +4072,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4115,32 +4086,38 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>150-årig sandtallskog, i renbetad nordvästsluttning</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>Sandtallskogsprojektet 2023, Västerbottens län</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112367987</v>
+        <v>87755085</v>
       </c>
       <c r="B33" t="n">
-        <v>93235</v>
+        <v>78993</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4148,34 +4125,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5966</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lögdeälven-Drakryggen m omnejd, Ång</t>
+          <t>Blåberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>690160</v>
+        <v>689857</v>
       </c>
       <c r="R33" t="n">
-        <v>7093472</v>
+        <v>7093888</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4202,12 +4182,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2020-08-23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2020-08-23</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4216,67 +4196,77 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>Sandtallskogsprojektet 2023, Västerbottens län</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112367930</v>
+        <v>89046268</v>
       </c>
       <c r="B34" t="n">
-        <v>57953</v>
+        <v>93213</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>2059</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lögdeälven-Drakryggen m omnejd, Ång</t>
+          <t>Blåberget, 1,6 km om toppen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>689998</v>
+        <v>689850</v>
       </c>
       <c r="R34" t="n">
-        <v>7093980</v>
+        <v>7093829</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4303,40 +4293,1334 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>barksprätt, ytliga ringhack gran</t>
+          <t>2020-08-31</t>
         </is>
       </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>140-årig sandtallskog</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>112367952</v>
+      </c>
+      <c r="B35" t="n">
+        <v>93213</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lögdeälven-Drakryggen m omnejd, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>689757</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7094522</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
           <t>Roger Olofsson</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
+      <c r="AX35" t="inlineStr">
         <is>
           <t>Roger Olofsson</t>
         </is>
       </c>
-      <c r="AY34" t="inlineStr">
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>87755147</v>
+      </c>
+      <c r="B36" t="n">
+        <v>93189</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Blåberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>689819</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7093761</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2020-08-23</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2020-08-23</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>87755103</v>
+      </c>
+      <c r="B37" t="n">
+        <v>93191</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Blåberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>689795</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7093764</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2020-08-23</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2020-08-23</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>89046267</v>
+      </c>
+      <c r="B38" t="n">
+        <v>93191</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Blåberget, 1,6 km om toppen, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>689819</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7093805</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2020-08-31</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2020-08-31</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>140-årig sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>89046270</v>
+      </c>
+      <c r="B39" t="n">
+        <v>93191</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Blåberget, 1,6 km om toppen, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>689854</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7093870</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2020-08-31</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2020-08-31</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>140-årig sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>89046271</v>
+      </c>
+      <c r="B40" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Blåberget, 1,6 km om toppen, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>689833</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7093948</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2020-08-31</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2020-08-31</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>140-årig sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>87755059</v>
+      </c>
+      <c r="B41" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Blåberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>689771</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7093769</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2020-08-23</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2020-08-23</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>89046269</v>
+      </c>
+      <c r="B42" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Blåberget, 1,6 km om toppen, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>689852</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7093854</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2020-08-31</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2020-08-31</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>140-årig sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>112368024</v>
+      </c>
+      <c r="B43" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lögdeälven-Drakryggen m omnejd, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>690157</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7093462</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>112367956</v>
+      </c>
+      <c r="B44" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lögdeälven-Drakryggen m omnejd, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>690157</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7093465</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>112367987</v>
+      </c>
+      <c r="B45" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lögdeälven-Drakryggen m omnejd, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>690160</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7093472</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Sandtallskogsprojektet 2023, Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>112367930</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lögdeälven-Drakryggen m omnejd, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>689998</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7093980</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>barksprätt, ytliga ringhack gran</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
         <is>
           <t>Sandtallskogsprojektet 2023, Västerbottens län</t>
         </is>
